--- a/output/property_feasibility.xlsx
+++ b/output/property_feasibility.xlsx
@@ -1723,7 +1723,7 @@
     </row>
     <row r="37" ht="16.5" customHeight="1"/>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="EE63"/>
   <mergeCells count="30">
     <mergeCell ref="D20:E20"/>
     <mergeCell ref="G10:I10"/>
@@ -2520,7 +2520,7 @@
     </row>
     <row r="37" ht="16.5" customHeight="1"/>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="EE63"/>
   <mergeCells count="30">
     <mergeCell ref="D20:E20"/>
     <mergeCell ref="G10:I10"/>
